--- a/artfynd/A 25404-2026 artfynd.xlsx
+++ b/artfynd/A 25404-2026 artfynd.xlsx
@@ -675,57 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110937694</v>
+        <v>65848188</v>
       </c>
       <c r="B2" t="n">
-        <v>95723</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Zakristorp, Dlr</t>
+          <t>Sakristorp S, Sakristorp, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540296.171901304</v>
+        <v>540251</v>
       </c>
       <c r="R2" t="n">
-        <v>6671676.592248245</v>
+        <v>6671356</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Finngården</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,56 +767,45 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Fuktigare f.d. odlingsmark kring gård</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Daniel Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Jansson, Lena Stigsdotter</t>
+          <t>Daniel Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65848188</v>
+        <v>117509552</v>
       </c>
       <c r="B3" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>102118</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,21 +820,25 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sakristorp S, Sakristorp, Dlr</t>
+          <t>Hällsjöbovägen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540250.8570332371</v>
+        <v>540111</v>
       </c>
       <c r="R3" t="n">
-        <v>6671355.660346061</v>
+        <v>6669776</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Finngården</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,49 +892,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Andersson</t>
+          <t>Pelle Adenäs</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Andersson</t>
+          <t>Pelle Adenäs, Göran Israelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117509552</v>
+        <v>91872855</v>
       </c>
       <c r="B4" t="n">
-        <v>56629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102118</v>
+        <v>102622</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -970,17 +947,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjöbovägen, Dlr</t>
+          <t>Hällsjöbovägen, Sakristorp, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540111</v>
+        <v>540161</v>
       </c>
       <c r="R4" t="n">
-        <v>6669776</v>
+        <v>6669714</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +981,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,12 +1011,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pelle Adenäs</t>
+          <t>Göran Israelsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pelle Adenäs, Göran Israelsson</t>
+          <t>Göran Israelsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 25404-2026 artfynd.xlsx
+++ b/artfynd/A 25404-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,60 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117509552</v>
+        <v>134600308</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102118</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjöbovägen, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540111</v>
+        <v>539933</v>
       </c>
       <c r="R3" t="n">
-        <v>6669776</v>
+        <v>6670104</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>23:50</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>23:50</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,69 +870,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Pelle Adenäs</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pelle Adenäs, Göran Israelsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91872855</v>
+        <v>134600457</v>
       </c>
       <c r="B4" t="n">
-        <v>57785</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102622</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjöbovägen, Sakristorp, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540161</v>
+        <v>539933</v>
       </c>
       <c r="R4" t="n">
-        <v>6669714</v>
+        <v>6670104</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +967,559 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134600272</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539971</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6670088</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134600265</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>539971</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6670088</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117509552</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällsjöbovägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>540111</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6669776</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pelle Adenäs</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pelle Adenäs, Göran Israelsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91872855</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällsjöbovägen, Sakristorp, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>540161</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6669714</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-03-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-03-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Göran Israelsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Göran Israelsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134600183</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>540081</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6670012</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal grov sälg med bohål.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25404-2026 artfynd.xlsx
+++ b/artfynd/A 25404-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65848188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600308</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600457</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600265</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117509552</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91872855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,8 +1560,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600183</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>